--- a/dati/tabella_aggiornamento_articoli.xlsx
+++ b/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D360A4D-4326-4A6F-A492-D89848148708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E162D3C-8681-46E2-930A-18E468564924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26430" yWindow="0" windowWidth="12010" windowHeight="13630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="72">
   <si>
     <t>Codice</t>
   </si>
@@ -214,53 +214,47 @@
     <t>6 Porzioni / Cartone</t>
   </si>
   <si>
-    <t>0 8 Fascette 160 20 Porzioni / Fascetta</t>
-  </si>
-  <si>
     <t>FI-Z-BI-L3-NA</t>
   </si>
   <si>
-    <t>Codice: 2-3-</t>
-  </si>
-  <si>
-    <t>SPECIALE 2 Finocchio biologico da porzionare</t>
-  </si>
-  <si>
-    <t>in classe - Data distribuzione: 30/03/2026</t>
-  </si>
-  <si>
-    <t>10,8 3 Colli 144 48 Porzioni / Collo</t>
-  </si>
-  <si>
     <t>ME-S-BI-L3-NA</t>
   </si>
   <si>
-    <t>Codice: 4-3-</t>
-  </si>
-  <si>
-    <t>SPECIALE 2 Mela biologica del territorio per</t>
-  </si>
-  <si>
-    <t>estratto - Data distribuzione: 30/03/2026</t>
-  </si>
-  <si>
-    <t>23,68 4 Colli 148 37 Porzioni / Collo</t>
-  </si>
-  <si>
     <t>10-FLYER Codice: --300326</t>
   </si>
   <si>
-    <t>Flyer programma - Data distribuzione: 30/03/2026</t>
+    <t>SPECIALE 2 Finocchio biologico da porzionare in classe</t>
+  </si>
+  <si>
+    <t>48 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>SPECIALE 2 Mela biologica del territorio per estratto</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>37 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>Flyer programma</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,12 +280,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -594,17 +592,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="1" max="1" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -629,7 +627,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -647,7 +645,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -663,7 +661,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -681,7 +679,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -707,7 +705,7 @@
       <c r="G5" s="1">
         <v>24</v>
       </c>
-      <c r="H5" s="1"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
@@ -723,7 +721,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -741,7 +739,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -767,7 +765,7 @@
       <c r="G8" s="1">
         <v>6</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
@@ -783,7 +781,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -809,7 +807,7 @@
       <c r="G10" s="1">
         <v>10</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
@@ -833,7 +831,7 @@
       <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
@@ -849,7 +847,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -867,7 +865,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -885,7 +883,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -911,7 +909,7 @@
       <c r="G15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -935,83 +933,56 @@
       <c r="G16" s="1">
         <v>6</v>
       </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="H18" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="H19" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>300326</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>300326</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dati/tabella_aggiornamento_articoli.xlsx
+++ b/dati/tabella_aggiornamento_articoli.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E162D3C-8681-46E2-930A-18E468564924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EE8DD0-122A-4CA2-8DDA-8BD6311BC8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32210" yWindow="930" windowWidth="18990" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
   <si>
     <t>Codice</t>
   </si>
@@ -239,6 +239,45 @@
   </si>
   <si>
     <t>Flyer programma</t>
+  </si>
+  <si>
+    <t>FR-M-BI-L3-NI</t>
+  </si>
+  <si>
+    <t>Mousse biologica di Fragola (51%) e Mela</t>
+  </si>
+  <si>
+    <t>10 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>LNS-04-GADGET</t>
+  </si>
+  <si>
+    <t>LNS-04-POSTER</t>
+  </si>
+  <si>
+    <t>Materiale promozionale - STICKER</t>
+  </si>
+  <si>
+    <t>Materiale informativo - POSTER</t>
+  </si>
+  <si>
+    <t>FVNS-03-MAGAZINE</t>
+  </si>
+  <si>
+    <t>FVNS-03-FOLDER</t>
+  </si>
+  <si>
+    <t>Folder misure</t>
+  </si>
+  <si>
+    <t>Magazine</t>
+  </si>
+  <si>
+    <t>50 Porzioni / Fascetta</t>
   </si>
 </sst>
 </file>
@@ -280,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -289,6 +328,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,11 +634,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" customWidth="1"/>
+    <col min="2" max="2" width="47.90625" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
@@ -978,7 +1020,77 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/dati/tabella_aggiornamento_articoli.xlsx
+++ b/dati/tabella_aggiornamento_articoli.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EE8DD0-122A-4CA2-8DDA-8BD6311BC8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274685E0-07BB-43C0-85EB-60674AB523B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32210" yWindow="930" windowWidth="18990" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Articoli!$A$1:$H$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="113">
   <si>
     <t>Codice</t>
   </si>
@@ -116,9 +119,6 @@
   </si>
   <si>
     <t>LT-AQ-04-LV</t>
-  </si>
-  <si>
-    <t>Latte Intero alta qualità (Data)</t>
   </si>
   <si>
     <t>6 Bottiglie / Fardello
@@ -278,6 +278,93 @@
   </si>
   <si>
     <t>50 Porzioni / Fascetta</t>
+  </si>
+  <si>
+    <t>Estrattore</t>
+  </si>
+  <si>
+    <t>10-AT-01</t>
+  </si>
+  <si>
+    <t>10-BICC</t>
+  </si>
+  <si>
+    <t>Bicchiere</t>
+  </si>
+  <si>
+    <t>10-CUCCH</t>
+  </si>
+  <si>
+    <t>Cucchiaini</t>
+  </si>
+  <si>
+    <t>10-PIATTO</t>
+  </si>
+  <si>
+    <t>Piattino</t>
+  </si>
+  <si>
+    <t>CA-Z-BI-L3-NA</t>
+  </si>
+  <si>
+    <t>SPECIALE</t>
+  </si>
+  <si>
+    <t>FO-DI-GP-01-NI</t>
+  </si>
+  <si>
+    <t>KI-S-BI-L3-NA</t>
+  </si>
+  <si>
+    <t>19 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>27 Porzioni / Collo</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Mela di Val di Non DOP</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>100 Porzioni / Confezione</t>
+  </si>
+  <si>
+    <t>1 Estrattore</t>
+  </si>
+  <si>
+    <t>Grana Padano DOP a cubetti</t>
+  </si>
+  <si>
+    <t>16 Buste / Collo</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Pera dell Emilia Romagna Igp</t>
+  </si>
+  <si>
+    <t>LT-AQ-04-LB</t>
+  </si>
+  <si>
+    <t>Latte Intero alta qualità</t>
+  </si>
+  <si>
+    <t>10 Bottiglie / Fardello</t>
+  </si>
+  <si>
+    <t>LT-AQ-04-LS</t>
+  </si>
+  <si>
+    <t>1 Busta</t>
   </si>
 </sst>
 </file>
@@ -634,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.36328125" customWidth="1"/>
@@ -645,6 +732,7 @@
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="14" style="3" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -674,367 +762,304 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
+      <c r="A2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="4" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="4" t="s">
-        <v>14</v>
+      <c r="A4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="1">
-        <v>24</v>
-      </c>
-      <c r="H5" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
       <c r="H6" s="4" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="1">
-        <v>6</v>
-      </c>
-      <c r="H11" s="4"/>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3">
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="4" t="s">
-        <v>52</v>
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="1">
-        <v>10</v>
-      </c>
-      <c r="H15" s="4"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="1">
-        <v>6</v>
-      </c>
-      <c r="H16" s="4"/>
+      <c r="A16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>65</v>
+      <c r="A17" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>83</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>67</v>
-      </c>
+      <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="H18" s="3">
-        <v>48</v>
+      <c r="G18" s="1"/>
+      <c r="H18" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+        <v>96</v>
+      </c>
       <c r="H19" s="3" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>72</v>
+      <c r="A20" t="s">
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B21" t="s">
@@ -1048,51 +1073,293 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
-        <v>77</v>
+      <c r="A22" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>109</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="1">
+        <v>6</v>
+      </c>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="1">
+        <v>10</v>
+      </c>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="1">
+        <v>6</v>
+      </c>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="H29" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+      <c r="A34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" s="1">
+        <v>10</v>
+      </c>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="1">
+        <v>6</v>
+      </c>
+      <c r="H35" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/dati/tabella_aggiornamento_articoli.xlsx
+++ b/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274685E0-07BB-43C0-85EB-60674AB523B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E214F6F-9675-4258-8760-CA015548DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -1092,7 +1092,7 @@
         <v>34</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -1160,7 +1160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>48</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="58" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>55</v>
       </c>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>59</v>
       </c>

--- a/dati/tabella_aggiornamento_articoli.xlsx
+++ b/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E214F6F-9675-4258-8760-CA015548DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9209A9F0-0828-4CCD-A47D-BBF6EB4FE8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Articoli" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="112">
   <si>
     <t>Codice</t>
   </si>
@@ -121,10 +121,6 @@
     <t>LT-AQ-04-LV</t>
   </si>
   <si>
-    <t>6 Bottiglie / Fardello
-6,6 Porzioni / Bottiglia</t>
-  </si>
-  <si>
     <t>Fardelli</t>
   </si>
   <si>
@@ -149,10 +145,6 @@
     <t>Latte Intero esl (Data)</t>
   </si>
   <si>
-    <t>10 Bottiglie / Fardello
-6,6 Porzioni / Bottiglia</t>
-  </si>
-  <si>
     <t>LT-ESL-IN-LB</t>
   </si>
   <si>
@@ -198,10 +190,6 @@
     <t>Yogurt naturale bianco bio intero (Data)</t>
   </si>
   <si>
-    <t>10 Cluster / Cartone
-2 Porzioni / Cluster</t>
-  </si>
-  <si>
     <t>Cluster</t>
   </si>
   <si>
@@ -365,6 +353,12 @@
   </si>
   <si>
     <t>1 Busta</t>
+  </si>
+  <si>
+    <t>2 Porzioni / Cluster</t>
+  </si>
+  <si>
+    <t>6,6 Porzioni / Bottiglia</t>
   </si>
 </sst>
 </file>
@@ -763,13 +757,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
@@ -777,24 +771,24 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>29</v>
@@ -823,10 +817,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -843,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -873,10 +867,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -911,27 +905,27 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
         <v>62</v>
       </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" s="3">
@@ -940,16 +934,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -972,27 +966,27 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
         <v>80</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>83</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>30</v>
@@ -1000,13 +994,13 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
         <v>79</v>
       </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>30</v>
@@ -1032,24 +1026,24 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
         <v>93</v>
       </c>
-      <c r="C19" t="s">
+      <c r="H19" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
         <v>29</v>
@@ -1060,10 +1054,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
         <v>29</v>
@@ -1074,22 +1068,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22">
         <v>12</v>
@@ -1097,45 +1091,45 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" s="1">
         <v>6</v>
@@ -1144,64 +1138,64 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C26" s="1" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" s="1">
         <v>10</v>
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G27" s="1">
         <v>6</v>
@@ -1210,79 +1204,79 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="H29" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="s">
         <v>48</v>
       </c>
-      <c r="B31" t="s">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>50</v>
-      </c>
       <c r="H31" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1294,27 +1288,27 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
         <v>52</v>
-      </c>
-      <c r="B33" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" t="s">
-        <v>54</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>21</v>
@@ -1323,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G34" s="1">
         <v>10</v>
@@ -1332,13 +1326,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>21</v>

--- a/dati/tabella_aggiornamento_articoli.xlsx
+++ b/dati/tabella_aggiornamento_articoli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9209A9F0-0828-4CCD-A47D-BBF6EB4FE8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA724D3-F05A-4207-8624-A55C46713140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="118">
   <si>
     <t>Codice</t>
   </si>
@@ -359,6 +359,24 @@
   </si>
   <si>
     <t>6,6 Porzioni / Bottiglia</t>
+  </si>
+  <si>
+    <t>FO-DI-AS-04-LV</t>
+  </si>
+  <si>
+    <t>ME-S-DI-L3-NA</t>
+  </si>
+  <si>
+    <t>SPECIALE 3 Mela di Val di Non DOP</t>
+  </si>
+  <si>
+    <t>SPECIALE 2 Asiago DOP</t>
+  </si>
+  <si>
+    <t>7,14 Porzioni / Fetta</t>
+  </si>
+  <si>
+    <t>7.14</t>
   </si>
 </sst>
 </file>
@@ -715,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.36328125" customWidth="1"/>
@@ -1348,6 +1366,34 @@
       </c>
       <c r="H35" s="4"/>
     </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H35">
